--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-05 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -730,7 +730,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>560470.62</v>
+        <v>560470.63</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>549889.12</v>
+        <v>549889.13</v>
       </c>
     </row>
     <row r="15">
@@ -866,7 +866,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>541526.12</v>
+        <v>541526.13</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>540380.62</v>
+        <v>540380.63</v>
       </c>
     </row>
     <row r="21">
@@ -1053,7 +1053,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>478339.12</v>
+        <v>478339.13</v>
       </c>
     </row>
     <row r="31">
